--- a/artfynd/A 47171-2023 artfynd.xlsx
+++ b/artfynd/A 47171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120513326</v>
+        <v>120513322</v>
       </c>
       <c r="B2" t="n">
-        <v>100194</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669604</v>
+        <v>669706</v>
       </c>
       <c r="R2" t="n">
-        <v>7010626</v>
+        <v>7010548</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120513322</v>
+        <v>120513326</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669706</v>
+        <v>669604</v>
       </c>
       <c r="R4" t="n">
-        <v>7010548</v>
+        <v>7010626</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 47171-2023 artfynd.xlsx
+++ b/artfynd/A 47171-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120513322</v>
+        <v>120513326</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>669706</v>
+        <v>669604</v>
       </c>
       <c r="R2" t="n">
-        <v>7010548</v>
+        <v>7010626</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120513323</v>
+        <v>120513322</v>
       </c>
       <c r="B3" t="n">
-        <v>79496</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>392</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>669687</v>
+        <v>669706</v>
       </c>
       <c r="R3" t="n">
-        <v>7010562</v>
+        <v>7010548</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120513326</v>
+        <v>120513323</v>
       </c>
       <c r="B4" t="n">
-        <v>100194</v>
+        <v>79496</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>392</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>669604</v>
+        <v>669687</v>
       </c>
       <c r="R4" t="n">
-        <v>7010626</v>
+        <v>7010562</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
